--- a/prueba_vf.xlsx
+++ b/prueba_vf.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SALA DE JUNTAS\Documents\program1\dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F14E637-EA83-42FA-8E67-506B468BC7F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30445C71-7727-44A2-BA57-D14FB1381E5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15390" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2104,17 +2104,27 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2143,28 +2153,18 @@
     <xf numFmtId="0" fontId="12" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="23">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2530,49 +2530,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="48.75" x14ac:dyDescent="0.6">
-      <c r="B1" s="46" t="s">
+      <c r="B1" s="50" t="s">
         <v>268</v>
       </c>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
-      <c r="E1" s="47"/>
-      <c r="F1" s="47"/>
-      <c r="G1" s="47"/>
-      <c r="H1" s="47"/>
-      <c r="I1" s="47"/>
-      <c r="J1" s="47"/>
-      <c r="K1" s="47"/>
-      <c r="L1" s="47"/>
-      <c r="M1" s="47"/>
-      <c r="N1" s="47"/>
-      <c r="O1" s="47"/>
-      <c r="P1" s="47"/>
-      <c r="Q1" s="47"/>
-      <c r="R1" s="47"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51"/>
+      <c r="G1" s="51"/>
+      <c r="H1" s="51"/>
+      <c r="I1" s="51"/>
+      <c r="J1" s="51"/>
+      <c r="K1" s="51"/>
+      <c r="L1" s="51"/>
+      <c r="M1" s="51"/>
+      <c r="N1" s="51"/>
+      <c r="O1" s="51"/>
+      <c r="P1" s="51"/>
+      <c r="Q1" s="51"/>
+      <c r="R1" s="51"/>
     </row>
     <row r="2" spans="1:18" ht="27.75" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B2" s="48" t="s">
+      <c r="B2" s="52" t="s">
         <v>267</v>
       </c>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
-      <c r="K2" s="48"/>
-      <c r="L2" s="48"/>
-      <c r="M2" s="48"/>
-      <c r="N2" s="48"/>
-      <c r="O2" s="48"/>
-      <c r="P2" s="48"/>
-      <c r="Q2" s="48"/>
-      <c r="R2" s="48"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="52"/>
+      <c r="K2" s="52"/>
+      <c r="L2" s="52"/>
+      <c r="M2" s="52"/>
+      <c r="N2" s="52"/>
+      <c r="O2" s="52"/>
+      <c r="P2" s="52"/>
+      <c r="Q2" s="52"/>
+      <c r="R2" s="52"/>
     </row>
     <row r="3" spans="1:18" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="49" t="s">
+      <c r="B3" s="53" t="s">
         <v>50</v>
       </c>
       <c r="C3" s="16" t="s">
@@ -2590,13 +2590,13 @@
       <c r="G3" s="15" t="s">
         <v>200</v>
       </c>
-      <c r="H3" s="50" t="s">
+      <c r="H3" s="54" t="s">
         <v>54</v>
       </c>
-      <c r="I3" s="51"/>
-      <c r="J3" s="52"/>
-      <c r="K3" s="53"/>
-      <c r="L3" s="54"/>
+      <c r="I3" s="55"/>
+      <c r="J3" s="56"/>
+      <c r="K3" s="57"/>
+      <c r="L3" s="58"/>
       <c r="M3" s="19" t="s">
         <v>55</v>
       </c>
@@ -2617,7 +2617,7 @@
       </c>
     </row>
     <row r="4" spans="1:18" ht="87" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="49"/>
+      <c r="B4" s="53"/>
       <c r="C4" s="34" t="s">
         <v>260</v>
       </c>
@@ -2955,13 +2955,13 @@
       <c r="G10" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="H10" s="55" t="s">
-        <v>85</v>
-      </c>
-      <c r="I10" s="56"/>
-      <c r="J10" s="56"/>
-      <c r="K10" s="56"/>
-      <c r="L10" s="57"/>
+      <c r="H10" s="44" t="s">
+        <v>85</v>
+      </c>
+      <c r="I10" s="45"/>
+      <c r="J10" s="45"/>
+      <c r="K10" s="45"/>
+      <c r="L10" s="46"/>
       <c r="M10" s="9" t="s">
         <v>85</v>
       </c>
@@ -3111,13 +3111,13 @@
       <c r="G13" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="H13" s="55" t="s">
-        <v>85</v>
-      </c>
-      <c r="I13" s="56"/>
-      <c r="J13" s="56"/>
-      <c r="K13" s="56"/>
-      <c r="L13" s="57"/>
+      <c r="H13" s="44" t="s">
+        <v>85</v>
+      </c>
+      <c r="I13" s="45"/>
+      <c r="J13" s="45"/>
+      <c r="K13" s="45"/>
+      <c r="L13" s="46"/>
       <c r="M13" s="8" t="s">
         <v>85</v>
       </c>
@@ -3156,13 +3156,13 @@
       <c r="G14" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="H14" s="55" t="s">
-        <v>85</v>
-      </c>
-      <c r="I14" s="56"/>
-      <c r="J14" s="56"/>
-      <c r="K14" s="56"/>
-      <c r="L14" s="57"/>
+      <c r="H14" s="44" t="s">
+        <v>85</v>
+      </c>
+      <c r="I14" s="45"/>
+      <c r="J14" s="45"/>
+      <c r="K14" s="45"/>
+      <c r="L14" s="46"/>
       <c r="M14" s="8" t="s">
         <v>85</v>
       </c>
@@ -3254,13 +3254,13 @@
       <c r="G16" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="H16" s="55" t="s">
-        <v>85</v>
-      </c>
-      <c r="I16" s="56"/>
-      <c r="J16" s="56"/>
-      <c r="K16" s="56"/>
-      <c r="L16" s="57"/>
+      <c r="H16" s="44" t="s">
+        <v>85</v>
+      </c>
+      <c r="I16" s="45"/>
+      <c r="J16" s="45"/>
+      <c r="K16" s="45"/>
+      <c r="L16" s="46"/>
       <c r="M16" s="8" t="s">
         <v>85</v>
       </c>
@@ -3352,13 +3352,13 @@
       <c r="G18" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="H18" s="55" t="s">
-        <v>85</v>
-      </c>
-      <c r="I18" s="56"/>
-      <c r="J18" s="56"/>
-      <c r="K18" s="56"/>
-      <c r="L18" s="57"/>
+      <c r="H18" s="44" t="s">
+        <v>85</v>
+      </c>
+      <c r="I18" s="45"/>
+      <c r="J18" s="45"/>
+      <c r="K18" s="45"/>
+      <c r="L18" s="46"/>
       <c r="M18" s="8" t="s">
         <v>85</v>
       </c>
@@ -3397,13 +3397,13 @@
       <c r="G19" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="H19" s="55" t="s">
-        <v>85</v>
-      </c>
-      <c r="I19" s="56"/>
-      <c r="J19" s="56"/>
-      <c r="K19" s="56"/>
-      <c r="L19" s="57"/>
+      <c r="H19" s="44" t="s">
+        <v>85</v>
+      </c>
+      <c r="I19" s="45"/>
+      <c r="J19" s="45"/>
+      <c r="K19" s="45"/>
+      <c r="L19" s="46"/>
       <c r="M19" s="8" t="s">
         <v>85</v>
       </c>
@@ -3445,13 +3445,13 @@
       <c r="G20" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="H20" s="55" t="s">
-        <v>85</v>
-      </c>
-      <c r="I20" s="56"/>
-      <c r="J20" s="56"/>
-      <c r="K20" s="56"/>
-      <c r="L20" s="57"/>
+      <c r="H20" s="44" t="s">
+        <v>85</v>
+      </c>
+      <c r="I20" s="45"/>
+      <c r="J20" s="45"/>
+      <c r="K20" s="45"/>
+      <c r="L20" s="46"/>
       <c r="M20" s="8" t="s">
         <v>85</v>
       </c>
@@ -3543,13 +3543,13 @@
       <c r="G22" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="H22" s="55" t="s">
-        <v>85</v>
-      </c>
-      <c r="I22" s="56"/>
-      <c r="J22" s="56"/>
-      <c r="K22" s="56"/>
-      <c r="L22" s="57"/>
+      <c r="H22" s="44" t="s">
+        <v>85</v>
+      </c>
+      <c r="I22" s="45"/>
+      <c r="J22" s="45"/>
+      <c r="K22" s="45"/>
+      <c r="L22" s="46"/>
       <c r="M22" s="8" t="s">
         <v>85</v>
       </c>
@@ -3641,13 +3641,13 @@
       <c r="G24" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="H24" s="55" t="s">
-        <v>85</v>
-      </c>
-      <c r="I24" s="56"/>
-      <c r="J24" s="56"/>
-      <c r="K24" s="56"/>
-      <c r="L24" s="57"/>
+      <c r="H24" s="44" t="s">
+        <v>85</v>
+      </c>
+      <c r="I24" s="45"/>
+      <c r="J24" s="45"/>
+      <c r="K24" s="45"/>
+      <c r="L24" s="46"/>
       <c r="M24" s="8" t="s">
         <v>85</v>
       </c>
@@ -3792,13 +3792,13 @@
       <c r="G27" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="H27" s="55" t="s">
-        <v>85</v>
-      </c>
-      <c r="I27" s="56"/>
-      <c r="J27" s="56"/>
-      <c r="K27" s="56"/>
-      <c r="L27" s="57"/>
+      <c r="H27" s="44" t="s">
+        <v>85</v>
+      </c>
+      <c r="I27" s="45"/>
+      <c r="J27" s="45"/>
+      <c r="K27" s="45"/>
+      <c r="L27" s="46"/>
       <c r="M27" s="8" t="s">
         <v>85</v>
       </c>
@@ -3837,13 +3837,13 @@
       <c r="G28" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="H28" s="55" t="s">
-        <v>85</v>
-      </c>
-      <c r="I28" s="56"/>
-      <c r="J28" s="56"/>
-      <c r="K28" s="56"/>
-      <c r="L28" s="57"/>
+      <c r="H28" s="44" t="s">
+        <v>85</v>
+      </c>
+      <c r="I28" s="45"/>
+      <c r="J28" s="45"/>
+      <c r="K28" s="45"/>
+      <c r="L28" s="46"/>
       <c r="M28" s="8" t="s">
         <v>85</v>
       </c>
@@ -4150,13 +4150,13 @@
       <c r="G34" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="H34" s="55" t="s">
-        <v>85</v>
-      </c>
-      <c r="I34" s="56"/>
-      <c r="J34" s="56"/>
-      <c r="K34" s="56"/>
-      <c r="L34" s="57"/>
+      <c r="H34" s="44" t="s">
+        <v>85</v>
+      </c>
+      <c r="I34" s="45"/>
+      <c r="J34" s="45"/>
+      <c r="K34" s="45"/>
+      <c r="L34" s="46"/>
       <c r="M34" s="8" t="s">
         <v>85</v>
       </c>
@@ -4251,13 +4251,13 @@
       <c r="G36" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="H36" s="55" t="s">
-        <v>85</v>
-      </c>
-      <c r="I36" s="56"/>
-      <c r="J36" s="56"/>
-      <c r="K36" s="56"/>
-      <c r="L36" s="57"/>
+      <c r="H36" s="44" t="s">
+        <v>85</v>
+      </c>
+      <c r="I36" s="45"/>
+      <c r="J36" s="45"/>
+      <c r="K36" s="45"/>
+      <c r="L36" s="46"/>
       <c r="M36" s="8" t="s">
         <v>85</v>
       </c>
@@ -4299,13 +4299,13 @@
       <c r="G37" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="H37" s="55" t="s">
-        <v>85</v>
-      </c>
-      <c r="I37" s="56"/>
-      <c r="J37" s="56"/>
-      <c r="K37" s="56"/>
-      <c r="L37" s="57"/>
+      <c r="H37" s="44" t="s">
+        <v>85</v>
+      </c>
+      <c r="I37" s="45"/>
+      <c r="J37" s="45"/>
+      <c r="K37" s="45"/>
+      <c r="L37" s="46"/>
       <c r="M37" s="8" t="s">
         <v>85</v>
       </c>
@@ -4347,13 +4347,13 @@
       <c r="G38" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="H38" s="55" t="s">
-        <v>85</v>
-      </c>
-      <c r="I38" s="56"/>
-      <c r="J38" s="56"/>
-      <c r="K38" s="56"/>
-      <c r="L38" s="57"/>
+      <c r="H38" s="44" t="s">
+        <v>85</v>
+      </c>
+      <c r="I38" s="45"/>
+      <c r="J38" s="45"/>
+      <c r="K38" s="45"/>
+      <c r="L38" s="46"/>
       <c r="M38" s="8" t="s">
         <v>85</v>
       </c>
@@ -4498,13 +4498,13 @@
       <c r="G41" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="H41" s="55" t="s">
-        <v>85</v>
-      </c>
-      <c r="I41" s="56"/>
-      <c r="J41" s="56"/>
-      <c r="K41" s="56"/>
-      <c r="L41" s="57"/>
+      <c r="H41" s="44" t="s">
+        <v>85</v>
+      </c>
+      <c r="I41" s="45"/>
+      <c r="J41" s="45"/>
+      <c r="K41" s="45"/>
+      <c r="L41" s="46"/>
       <c r="M41" s="9" t="s">
         <v>85</v>
       </c>
@@ -4535,13 +4535,13 @@
       <c r="G42" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="H42" s="55" t="s">
-        <v>85</v>
-      </c>
-      <c r="I42" s="56"/>
-      <c r="J42" s="56"/>
-      <c r="K42" s="56"/>
-      <c r="L42" s="57"/>
+      <c r="H42" s="44" t="s">
+        <v>85</v>
+      </c>
+      <c r="I42" s="45"/>
+      <c r="J42" s="45"/>
+      <c r="K42" s="45"/>
+      <c r="L42" s="46"/>
       <c r="M42" s="9" t="s">
         <v>85</v>
       </c>
@@ -4572,13 +4572,13 @@
       <c r="G43" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="H43" s="55" t="s">
-        <v>85</v>
-      </c>
-      <c r="I43" s="56"/>
-      <c r="J43" s="56"/>
-      <c r="K43" s="56"/>
-      <c r="L43" s="57"/>
+      <c r="H43" s="44" t="s">
+        <v>85</v>
+      </c>
+      <c r="I43" s="45"/>
+      <c r="J43" s="45"/>
+      <c r="K43" s="45"/>
+      <c r="L43" s="46"/>
       <c r="M43" s="8" t="s">
         <v>85</v>
       </c>
@@ -4673,13 +4673,13 @@
       <c r="G45" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="H45" s="55" t="s">
-        <v>85</v>
-      </c>
-      <c r="I45" s="56"/>
-      <c r="J45" s="56"/>
-      <c r="K45" s="56"/>
-      <c r="L45" s="57"/>
+      <c r="H45" s="44" t="s">
+        <v>85</v>
+      </c>
+      <c r="I45" s="45"/>
+      <c r="J45" s="45"/>
+      <c r="K45" s="45"/>
+      <c r="L45" s="46"/>
       <c r="M45" s="8" t="s">
         <v>85</v>
       </c>
@@ -4721,13 +4721,13 @@
       <c r="G46" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="H46" s="55" t="s">
-        <v>85</v>
-      </c>
-      <c r="I46" s="56"/>
-      <c r="J46" s="56"/>
-      <c r="K46" s="56"/>
-      <c r="L46" s="57"/>
+      <c r="H46" s="44" t="s">
+        <v>85</v>
+      </c>
+      <c r="I46" s="45"/>
+      <c r="J46" s="45"/>
+      <c r="K46" s="45"/>
+      <c r="L46" s="46"/>
       <c r="M46" s="8" t="s">
         <v>85</v>
       </c>
@@ -4769,13 +4769,13 @@
       <c r="G47" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="H47" s="55" t="s">
-        <v>85</v>
-      </c>
-      <c r="I47" s="56"/>
-      <c r="J47" s="56"/>
-      <c r="K47" s="56"/>
-      <c r="L47" s="57"/>
+      <c r="H47" s="44" t="s">
+        <v>85</v>
+      </c>
+      <c r="I47" s="45"/>
+      <c r="J47" s="45"/>
+      <c r="K47" s="45"/>
+      <c r="L47" s="46"/>
       <c r="M47" s="8" t="s">
         <v>85</v>
       </c>
@@ -4923,13 +4923,13 @@
       <c r="G50" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="H50" s="55" t="s">
-        <v>85</v>
-      </c>
-      <c r="I50" s="56"/>
-      <c r="J50" s="56"/>
-      <c r="K50" s="56"/>
-      <c r="L50" s="57"/>
+      <c r="H50" s="44" t="s">
+        <v>85</v>
+      </c>
+      <c r="I50" s="45"/>
+      <c r="J50" s="45"/>
+      <c r="K50" s="45"/>
+      <c r="L50" s="46"/>
       <c r="M50" s="8" t="s">
         <v>85</v>
       </c>
@@ -4971,13 +4971,13 @@
       <c r="G51" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="H51" s="55" t="s">
-        <v>85</v>
-      </c>
-      <c r="I51" s="56"/>
-      <c r="J51" s="56"/>
-      <c r="K51" s="56"/>
-      <c r="L51" s="57"/>
+      <c r="H51" s="44" t="s">
+        <v>85</v>
+      </c>
+      <c r="I51" s="45"/>
+      <c r="J51" s="45"/>
+      <c r="K51" s="45"/>
+      <c r="L51" s="46"/>
       <c r="M51" s="8" t="s">
         <v>85</v>
       </c>
@@ -5067,13 +5067,13 @@
       <c r="G53" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="H53" s="55" t="s">
-        <v>85</v>
-      </c>
-      <c r="I53" s="56"/>
-      <c r="J53" s="56"/>
-      <c r="K53" s="56"/>
-      <c r="L53" s="57"/>
+      <c r="H53" s="44" t="s">
+        <v>85</v>
+      </c>
+      <c r="I53" s="45"/>
+      <c r="J53" s="45"/>
+      <c r="K53" s="45"/>
+      <c r="L53" s="46"/>
       <c r="M53" s="8" t="s">
         <v>85</v>
       </c>
@@ -5168,13 +5168,13 @@
       <c r="G55" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="H55" s="55" t="s">
-        <v>85</v>
-      </c>
-      <c r="I55" s="56"/>
-      <c r="J55" s="56"/>
-      <c r="K55" s="56"/>
-      <c r="L55" s="57"/>
+      <c r="H55" s="44" t="s">
+        <v>85</v>
+      </c>
+      <c r="I55" s="45"/>
+      <c r="J55" s="45"/>
+      <c r="K55" s="45"/>
+      <c r="L55" s="46"/>
       <c r="M55" s="8" t="s">
         <v>85</v>
       </c>
@@ -5365,13 +5365,13 @@
       <c r="G59" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="H59" s="55" t="s">
-        <v>85</v>
-      </c>
-      <c r="I59" s="56"/>
-      <c r="J59" s="56"/>
-      <c r="K59" s="56"/>
-      <c r="L59" s="57"/>
+      <c r="H59" s="44" t="s">
+        <v>85</v>
+      </c>
+      <c r="I59" s="45"/>
+      <c r="J59" s="45"/>
+      <c r="K59" s="45"/>
+      <c r="L59" s="46"/>
       <c r="M59" s="8" t="s">
         <v>85</v>
       </c>
@@ -5943,13 +5943,13 @@
       <c r="G70" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="H70" s="55" t="s">
-        <v>85</v>
-      </c>
-      <c r="I70" s="56"/>
-      <c r="J70" s="56"/>
-      <c r="K70" s="56"/>
-      <c r="L70" s="57"/>
+      <c r="H70" s="44" t="s">
+        <v>85</v>
+      </c>
+      <c r="I70" s="45"/>
+      <c r="J70" s="45"/>
+      <c r="K70" s="45"/>
+      <c r="L70" s="46"/>
       <c r="M70" s="8" t="s">
         <v>85</v>
       </c>
@@ -5991,13 +5991,13 @@
       <c r="G71" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="H71" s="55" t="s">
-        <v>85</v>
-      </c>
-      <c r="I71" s="56"/>
-      <c r="J71" s="56"/>
-      <c r="K71" s="56"/>
-      <c r="L71" s="57"/>
+      <c r="H71" s="44" t="s">
+        <v>85</v>
+      </c>
+      <c r="I71" s="45"/>
+      <c r="J71" s="45"/>
+      <c r="K71" s="45"/>
+      <c r="L71" s="46"/>
       <c r="M71" s="8" t="s">
         <v>85</v>
       </c>
@@ -6198,13 +6198,13 @@
       <c r="G75" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="H75" s="58" t="s">
-        <v>85</v>
-      </c>
-      <c r="I75" s="59"/>
-      <c r="J75" s="59"/>
-      <c r="K75" s="59"/>
-      <c r="L75" s="60"/>
+      <c r="H75" s="47" t="s">
+        <v>85</v>
+      </c>
+      <c r="I75" s="48"/>
+      <c r="J75" s="48"/>
+      <c r="K75" s="48"/>
+      <c r="L75" s="49"/>
       <c r="M75" s="8" t="s">
         <v>85</v>
       </c>
@@ -6230,6 +6230,23 @@
   </sheetData>
   <autoFilter ref="B4:R75" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="33">
+    <mergeCell ref="H45:L45"/>
+    <mergeCell ref="H16:L16"/>
+    <mergeCell ref="H41:L41"/>
+    <mergeCell ref="H42:L42"/>
+    <mergeCell ref="B1:R1"/>
+    <mergeCell ref="B2:R2"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="H36:L36"/>
+    <mergeCell ref="H34:L34"/>
+    <mergeCell ref="H27:L27"/>
+    <mergeCell ref="H13:L13"/>
+    <mergeCell ref="H14:L14"/>
+    <mergeCell ref="H18:L18"/>
+    <mergeCell ref="H19:L19"/>
+    <mergeCell ref="H20:L20"/>
+    <mergeCell ref="H22:L22"/>
     <mergeCell ref="H46:L46"/>
     <mergeCell ref="H28:L28"/>
     <mergeCell ref="H24:L24"/>
@@ -6246,23 +6263,6 @@
     <mergeCell ref="H37:L37"/>
     <mergeCell ref="H38:L38"/>
     <mergeCell ref="H43:L43"/>
-    <mergeCell ref="B1:R1"/>
-    <mergeCell ref="B2:R2"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="H36:L36"/>
-    <mergeCell ref="H34:L34"/>
-    <mergeCell ref="H27:L27"/>
-    <mergeCell ref="H13:L13"/>
-    <mergeCell ref="H14:L14"/>
-    <mergeCell ref="H18:L18"/>
-    <mergeCell ref="H19:L19"/>
-    <mergeCell ref="H20:L20"/>
-    <mergeCell ref="H22:L22"/>
-    <mergeCell ref="H45:L45"/>
-    <mergeCell ref="H16:L16"/>
-    <mergeCell ref="H41:L41"/>
-    <mergeCell ref="H42:L42"/>
   </mergeCells>
   <pageMargins left="0" right="0" top="0.39370078740157483" bottom="0" header="0" footer="0"/>
   <pageSetup scale="39" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -6301,49 +6301,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="48.75" x14ac:dyDescent="0.6">
-      <c r="B1" s="46" t="s">
+      <c r="B1" s="50" t="s">
         <v>268</v>
       </c>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
-      <c r="E1" s="47"/>
-      <c r="F1" s="47"/>
-      <c r="G1" s="47"/>
-      <c r="H1" s="47"/>
-      <c r="I1" s="47"/>
-      <c r="J1" s="47"/>
-      <c r="K1" s="47"/>
-      <c r="L1" s="47"/>
-      <c r="M1" s="47"/>
-      <c r="N1" s="47"/>
-      <c r="O1" s="47"/>
-      <c r="P1" s="47"/>
-      <c r="Q1" s="47"/>
-      <c r="R1" s="47"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51"/>
+      <c r="G1" s="51"/>
+      <c r="H1" s="51"/>
+      <c r="I1" s="51"/>
+      <c r="J1" s="51"/>
+      <c r="K1" s="51"/>
+      <c r="L1" s="51"/>
+      <c r="M1" s="51"/>
+      <c r="N1" s="51"/>
+      <c r="O1" s="51"/>
+      <c r="P1" s="51"/>
+      <c r="Q1" s="51"/>
+      <c r="R1" s="51"/>
     </row>
     <row r="2" spans="1:18" ht="27.75" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B2" s="48" t="s">
+      <c r="B2" s="52" t="s">
         <v>321</v>
       </c>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
-      <c r="K2" s="48"/>
-      <c r="L2" s="48"/>
-      <c r="M2" s="48"/>
-      <c r="N2" s="48"/>
-      <c r="O2" s="48"/>
-      <c r="P2" s="48"/>
-      <c r="Q2" s="48"/>
-      <c r="R2" s="48"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="52"/>
+      <c r="K2" s="52"/>
+      <c r="L2" s="52"/>
+      <c r="M2" s="52"/>
+      <c r="N2" s="52"/>
+      <c r="O2" s="52"/>
+      <c r="P2" s="52"/>
+      <c r="Q2" s="52"/>
+      <c r="R2" s="52"/>
     </row>
     <row r="3" spans="1:18" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="49" t="s">
+      <c r="B3" s="53" t="s">
         <v>298</v>
       </c>
       <c r="C3" s="15" t="s">
@@ -6361,13 +6361,13 @@
       <c r="G3" s="15" t="s">
         <v>200</v>
       </c>
-      <c r="H3" s="50" t="s">
+      <c r="H3" s="54" t="s">
         <v>54</v>
       </c>
-      <c r="I3" s="51"/>
-      <c r="J3" s="52"/>
-      <c r="K3" s="53"/>
-      <c r="L3" s="54"/>
+      <c r="I3" s="55"/>
+      <c r="J3" s="56"/>
+      <c r="K3" s="57"/>
+      <c r="L3" s="58"/>
       <c r="M3" s="19" t="s">
         <v>55</v>
       </c>
@@ -6388,7 +6388,7 @@
       </c>
     </row>
     <row r="4" spans="1:18" ht="87" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="49"/>
+      <c r="B4" s="53"/>
       <c r="C4" s="34" t="s">
         <v>260</v>
       </c>
@@ -6439,28 +6439,28 @@
       </c>
     </row>
     <row r="5" spans="1:18" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="43" t="s">
+      <c r="B5" s="60" t="s">
         <v>302</v>
       </c>
-      <c r="C5" s="44"/>
-      <c r="D5" s="44"/>
-      <c r="E5" s="44"/>
-      <c r="F5" s="44"/>
-      <c r="G5" s="44"/>
-      <c r="H5" s="44"/>
-      <c r="I5" s="44"/>
-      <c r="J5" s="44"/>
-      <c r="K5" s="44"/>
-      <c r="L5" s="44"/>
-      <c r="M5" s="44"/>
-      <c r="N5" s="44"/>
-      <c r="O5" s="44"/>
-      <c r="P5" s="44"/>
-      <c r="Q5" s="44"/>
-      <c r="R5" s="45"/>
+      <c r="C5" s="61"/>
+      <c r="D5" s="61"/>
+      <c r="E5" s="61"/>
+      <c r="F5" s="61"/>
+      <c r="G5" s="61"/>
+      <c r="H5" s="61"/>
+      <c r="I5" s="61"/>
+      <c r="J5" s="61"/>
+      <c r="K5" s="61"/>
+      <c r="L5" s="61"/>
+      <c r="M5" s="61"/>
+      <c r="N5" s="61"/>
+      <c r="O5" s="61"/>
+      <c r="P5" s="61"/>
+      <c r="Q5" s="61"/>
+      <c r="R5" s="62"/>
     </row>
     <row r="6" spans="1:18" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="42"/>
+      <c r="A6" s="59"/>
       <c r="B6" s="41" t="s">
         <v>310</v>
       </c>
@@ -6514,7 +6514,7 @@
       </c>
     </row>
     <row r="7" spans="1:18" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="42"/>
+      <c r="A7" s="59"/>
       <c r="B7" s="41" t="s">
         <v>300</v>
       </c>
@@ -6568,7 +6568,7 @@
       </c>
     </row>
     <row r="8" spans="1:18" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="42"/>
+      <c r="A8" s="59"/>
       <c r="B8" s="41" t="s">
         <v>299</v>
       </c>
@@ -6622,35 +6622,35 @@
       </c>
     </row>
     <row r="9" spans="1:18" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="43" t="s">
+      <c r="B9" s="60" t="s">
         <v>303</v>
       </c>
-      <c r="C9" s="44"/>
-      <c r="D9" s="44"/>
-      <c r="E9" s="44"/>
-      <c r="F9" s="44"/>
-      <c r="G9" s="44"/>
-      <c r="H9" s="44"/>
-      <c r="I9" s="44"/>
-      <c r="J9" s="44"/>
-      <c r="K9" s="44"/>
-      <c r="L9" s="44"/>
-      <c r="M9" s="44" t="s">
-        <v>85</v>
-      </c>
-      <c r="N9" s="44" t="s">
-        <v>74</v>
-      </c>
-      <c r="O9" s="44" t="s">
+      <c r="C9" s="61"/>
+      <c r="D9" s="61"/>
+      <c r="E9" s="61"/>
+      <c r="F9" s="61"/>
+      <c r="G9" s="61"/>
+      <c r="H9" s="61"/>
+      <c r="I9" s="61"/>
+      <c r="J9" s="61"/>
+      <c r="K9" s="61"/>
+      <c r="L9" s="61"/>
+      <c r="M9" s="61" t="s">
+        <v>85</v>
+      </c>
+      <c r="N9" s="61" t="s">
+        <v>74</v>
+      </c>
+      <c r="O9" s="61" t="s">
         <v>209</v>
       </c>
-      <c r="P9" s="44" t="s">
+      <c r="P9" s="61" t="s">
         <v>209</v>
       </c>
-      <c r="Q9" s="44" t="s">
+      <c r="Q9" s="61" t="s">
         <v>209</v>
       </c>
-      <c r="R9" s="45" t="s">
+      <c r="R9" s="62" t="s">
         <v>209</v>
       </c>
     </row>
@@ -6761,45 +6761,45 @@
       </c>
     </row>
     <row r="12" spans="1:18" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="43" t="s">
+      <c r="B12" s="60" t="s">
         <v>304</v>
       </c>
-      <c r="C12" s="44"/>
-      <c r="D12" s="44"/>
-      <c r="E12" s="44"/>
-      <c r="F12" s="44"/>
-      <c r="G12" s="44"/>
-      <c r="H12" s="44" t="s">
+      <c r="C12" s="61"/>
+      <c r="D12" s="61"/>
+      <c r="E12" s="61"/>
+      <c r="F12" s="61"/>
+      <c r="G12" s="61"/>
+      <c r="H12" s="61" t="s">
         <v>214</v>
       </c>
-      <c r="I12" s="44" t="s">
-        <v>74</v>
-      </c>
-      <c r="J12" s="44" t="s">
-        <v>74</v>
-      </c>
-      <c r="K12" s="44" t="s">
-        <v>74</v>
-      </c>
-      <c r="L12" s="44" t="s">
-        <v>74</v>
-      </c>
-      <c r="M12" s="44" t="s">
-        <v>74</v>
-      </c>
-      <c r="N12" s="44" t="s">
+      <c r="I12" s="61" t="s">
+        <v>74</v>
+      </c>
+      <c r="J12" s="61" t="s">
+        <v>74</v>
+      </c>
+      <c r="K12" s="61" t="s">
+        <v>74</v>
+      </c>
+      <c r="L12" s="61" t="s">
+        <v>74</v>
+      </c>
+      <c r="M12" s="61" t="s">
+        <v>74</v>
+      </c>
+      <c r="N12" s="61" t="s">
         <v>188</v>
       </c>
-      <c r="O12" s="44" t="s">
+      <c r="O12" s="61" t="s">
         <v>223</v>
       </c>
-      <c r="P12" s="44" t="s">
+      <c r="P12" s="61" t="s">
         <v>223</v>
       </c>
-      <c r="Q12" s="44" t="s">
+      <c r="Q12" s="61" t="s">
         <v>223</v>
       </c>
-      <c r="R12" s="45" t="s">
+      <c r="R12" s="62" t="s">
         <v>223</v>
       </c>
     </row>
@@ -7122,53 +7122,53 @@
       </c>
     </row>
     <row r="19" spans="2:18" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="43" t="s">
+      <c r="B19" s="60" t="s">
         <v>305</v>
       </c>
-      <c r="C19" s="44" t="s">
+      <c r="C19" s="61" t="s">
         <v>149</v>
       </c>
-      <c r="D19" s="44" t="s">
-        <v>74</v>
-      </c>
-      <c r="E19" s="44"/>
-      <c r="F19" s="44" t="s">
+      <c r="D19" s="61" t="s">
+        <v>74</v>
+      </c>
+      <c r="E19" s="61"/>
+      <c r="F19" s="61" t="s">
         <v>118</v>
       </c>
-      <c r="G19" s="44" t="s">
+      <c r="G19" s="61" t="s">
         <v>142</v>
       </c>
-      <c r="H19" s="44" t="s">
+      <c r="H19" s="61" t="s">
         <v>82</v>
       </c>
-      <c r="I19" s="44" t="s">
-        <v>74</v>
-      </c>
-      <c r="J19" s="44" t="s">
-        <v>74</v>
-      </c>
-      <c r="K19" s="44" t="s">
-        <v>74</v>
-      </c>
-      <c r="L19" s="44" t="s">
+      <c r="I19" s="61" t="s">
+        <v>74</v>
+      </c>
+      <c r="J19" s="61" t="s">
+        <v>74</v>
+      </c>
+      <c r="K19" s="61" t="s">
+        <v>74</v>
+      </c>
+      <c r="L19" s="61" t="s">
         <v>179</v>
       </c>
-      <c r="M19" s="44" t="s">
-        <v>85</v>
-      </c>
-      <c r="N19" s="44" t="s">
+      <c r="M19" s="61" t="s">
+        <v>85</v>
+      </c>
+      <c r="N19" s="61" t="s">
         <v>192</v>
       </c>
-      <c r="O19" s="44" t="s">
+      <c r="O19" s="61" t="s">
         <v>231</v>
       </c>
-      <c r="P19" s="44" t="s">
+      <c r="P19" s="61" t="s">
         <v>231</v>
       </c>
-      <c r="Q19" s="44" t="s">
+      <c r="Q19" s="61" t="s">
         <v>231</v>
       </c>
-      <c r="R19" s="45" t="s">
+      <c r="R19" s="62" t="s">
         <v>231</v>
       </c>
     </row>
@@ -7221,7 +7221,7 @@
       <c r="Q20" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="R20" s="61" t="s">
+      <c r="R20" s="42" t="s">
         <v>231</v>
       </c>
     </row>
@@ -7274,7 +7274,7 @@
       <c r="Q21" s="3" t="s">
         <v>337</v>
       </c>
-      <c r="R21" s="61" t="s">
+      <c r="R21" s="42" t="s">
         <v>337</v>
       </c>
     </row>
@@ -7321,20 +7321,20 @@
     </row>
     <row r="26" spans="2:18" ht="20.25" x14ac:dyDescent="0.3">
       <c r="B26" s="1"/>
-      <c r="L26" s="62"/>
+      <c r="L26" s="43"/>
     </row>
   </sheetData>
   <autoFilter ref="B4:R23" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <mergeCells count="9">
+    <mergeCell ref="B9:R9"/>
+    <mergeCell ref="B12:R12"/>
+    <mergeCell ref="B19:R19"/>
     <mergeCell ref="B1:R1"/>
     <mergeCell ref="B2:R2"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="H3:L3"/>
     <mergeCell ref="A6:A8"/>
     <mergeCell ref="B5:R5"/>
-    <mergeCell ref="B9:R9"/>
-    <mergeCell ref="B12:R12"/>
-    <mergeCell ref="B19:R19"/>
   </mergeCells>
   <phoneticPr fontId="24" type="noConversion"/>
   <pageMargins left="0" right="0" top="0.39370078740157483" bottom="0" header="0" footer="0"/>
